--- a/tests/test_vacancies.xlsx
+++ b/tests/test_vacancies.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,25 +441,35 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>name_companies</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>url_companies</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>salary_from</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>salary_to</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>city</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>requirement</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>work_format</t>
         </is>
@@ -478,25 +488,35 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://hh.ru/4567890</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>100000</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Москва</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Знание основ программирования.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Гибрид</t>
         </is>
